--- a/data/trending_integrated_20260923_14.xlsx
+++ b/data/trending_integrated_20260923_14.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>토마토시스템</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1942</v>
+        <v>4035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.15%</t>
+          <t>'+21.72%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.39</v>
+        <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="F2" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="H2" t="n">
-        <v>1.02</v>
+        <v>1.63</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1603</v>
+        <v>3315</v>
       </c>
       <c r="K2" t="n">
-        <v>1603</v>
+        <v>3310</v>
       </c>
       <c r="L2" t="n">
-        <v>2030</v>
+        <v>4305</v>
       </c>
       <c r="M2" t="n">
-        <v>1585</v>
+        <v>3070</v>
       </c>
       <c r="N2" t="n">
-        <v>1.41</v>
+        <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>55299412580</v>
+        <v>41944211165</v>
       </c>
       <c r="P2" t="n">
-        <v>2465</v>
+        <v>6950</v>
       </c>
       <c r="Q2" t="n">
-        <v>865</v>
+        <v>1809</v>
       </c>
       <c r="R2" t="n">
-        <v>-358000</v>
+        <v>-3000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 특허 플렉시블 PCB 확보 및 AI 데이터센터향 공급 확대 소식 기반의 주가 상승 기대.</t>
+          <t>3연상 기록, 엔트로픽 의료AI 관련 기대감 있으나 급락 가능성 언급. 개인 투자자 위주 거래.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['플렉시블 PCB', 'AI 데이터센터']</t>
+          <t>['3연상', '의료AI', '개인매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>393210</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>토마토시스템</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4015</v>
+        <v>1902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.12%</t>
+          <t>'+18.65%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.02</v>
+        <v>-0.39</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="H3" t="n">
-        <v>1.63</v>
+        <v>1.02</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3315</v>
+        <v>1603</v>
       </c>
       <c r="K3" t="n">
-        <v>3310</v>
+        <v>1603</v>
       </c>
       <c r="L3" t="n">
-        <v>4305</v>
+        <v>2030</v>
       </c>
       <c r="M3" t="n">
-        <v>3070</v>
+        <v>1585</v>
       </c>
       <c r="N3" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="O3" t="n">
-        <v>41162585621</v>
+        <v>56497031014</v>
       </c>
       <c r="P3" t="n">
-        <v>6950</v>
+        <v>2465</v>
       </c>
       <c r="Q3" t="n">
-        <v>1809</v>
+        <v>865</v>
       </c>
       <c r="R3" t="n">
-        <v>-3000</v>
+        <v>-358000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3연상 기록, 엔트로픽 의료AI 관련 기대감 있으나 급락 가능성 언급. 개인 투자자 위주 거래.</t>
+          <t>미국 특허 플렉시블 PCB 확보 및 AI 데이터센터향 공급 확대 소식 기반의 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['3연상', '의료AI', '개인매수']</t>
+          <t>['플렉시블 PCB', 'AI 데이터센터']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>393210</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17700</v>
+        <v>17760</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.05%</t>
+          <t>'+14.43%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F4" t="n">
         <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H4" t="n">
         <v>0.6</v>
@@ -794,7 +794,7 @@
         <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>93089953855</v>
+        <v>93406078445</v>
       </c>
       <c r="P4" t="n">
         <v>34650</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>스페이스X 선정 및 NASA 우주 임무 적합 장비 선정 기반의 포터블 X-Ray 시장 도전 및 주가 급등.</t>
+          <t>스페이스X 우주 임무 선정 및 인도발 수주 등 강력한 호재 기반으로 한 레메디의 급등세 전망. 기술력 검증 및 시장 확대 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['포터블 X-Ray', '스페이스X']</t>
+          <t>['스페이스X', '엑스레이', '수주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14640</v>
+        <v>14660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.62%</t>
+          <t>'+12.51%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.42</v>
+        <v>-0.9</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H5" t="n">
-        <v>0.86</v>
+        <v>1.89</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13000</v>
+        <v>13030</v>
       </c>
       <c r="K5" t="n">
-        <v>12870</v>
+        <v>12850</v>
       </c>
       <c r="L5" t="n">
-        <v>15900</v>
+        <v>16420</v>
       </c>
       <c r="M5" t="n">
-        <v>12650</v>
+        <v>12660</v>
       </c>
       <c r="N5" t="n">
-        <v>0.44</v>
+        <v>2.79</v>
       </c>
       <c r="O5" t="n">
-        <v>163678497020</v>
+        <v>119570389805</v>
       </c>
       <c r="P5" t="n">
-        <v>25700</v>
+        <v>64600</v>
       </c>
       <c r="Q5" t="n">
-        <v>4600</v>
+        <v>7520</v>
       </c>
       <c r="R5" t="n">
-        <v>84000</v>
+        <v>2000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
+          <t>초소형위성 국방과제 주관 등 사업 모멘텀에 대한 기대감과 함께 주가 하락 및 투경 관련 우려가 공존함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['2차상승', '단기과열', '명절효과']</t>
+          <t>['나라스페이스', '초소형위성', '우주항공']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>478340</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14250</v>
+        <v>14440</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.36%</t>
+          <t>'+11.08%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.9</v>
+        <v>0.42</v>
       </c>
       <c r="E6" t="n">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="H6" t="n">
-        <v>1.89</v>
+        <v>0.86</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13030</v>
+        <v>13000</v>
       </c>
       <c r="K6" t="n">
-        <v>12850</v>
+        <v>12870</v>
       </c>
       <c r="L6" t="n">
-        <v>16420</v>
+        <v>15900</v>
       </c>
       <c r="M6" t="n">
-        <v>12660</v>
+        <v>12650</v>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>0.44</v>
       </c>
       <c r="O6" t="n">
-        <v>109679184725</v>
+        <v>164611551915</v>
       </c>
       <c r="P6" t="n">
-        <v>64600</v>
+        <v>25700</v>
       </c>
       <c r="Q6" t="n">
-        <v>7520</v>
+        <v>4600</v>
       </c>
       <c r="R6" t="n">
-        <v>2000</v>
+        <v>84000</v>
       </c>
       <c r="S6" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>초소형위성 국방과제 주관 등 사업 모멘텀에 대한 기대감과 함께 주가 하락 및 투경 관련 우려가 공존함.</t>
+          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['나라스페이스', '초소형위성', '우주항공']</t>
+          <t>['2차상승', '단기과열', '명절효과']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>478340</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18060</v>
+        <v>18170</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.19%</t>
+          <t>'+9.85%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F7" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G7" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="H7" t="n">
         <v>0.62</v>
@@ -1070,7 +1070,7 @@
         <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>301506154855</v>
+        <v>302924285370</v>
       </c>
       <c r="P7" t="n">
         <v>30550</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>220000</v>
+        <v>219750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.02%</t>
+          <t>'+3.90%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>415</v>
+        <v>450</v>
       </c>
       <c r="H8" t="n">
         <v>75.51000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>75.5</v>
       </c>
       <c r="O8" t="n">
-        <v>855654678500</v>
+        <v>879746824500</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7840</v>
+        <v>7820</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.02%</t>
+          <t>'+2.76%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H9" t="n">
         <v>1.9</v>
@@ -1254,7 +1254,7 @@
         <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>89490449180</v>
+        <v>89738678160</v>
       </c>
       <c r="P9" t="n">
         <v>16200</v>
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G10" t="n">
-        <v>1909</v>
+        <v>1919</v>
       </c>
       <c r="H10" t="n">
         <v>46.55</v>
@@ -1346,7 +1346,7 @@
         <v>46.56</v>
       </c>
       <c r="O10" t="n">
-        <v>3639784605750</v>
+        <v>3770998262250</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13940</v>
+        <v>13930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.50%</t>
+          <t>'+2.43%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
         <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H11" t="n">
         <v>9.609999999999999</v>
@@ -1438,7 +1438,7 @@
         <v>9.77</v>
       </c>
       <c r="O11" t="n">
-        <v>97657697475</v>
+        <v>98430672720</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1849000</v>
+        <v>8530</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.49%</t>
+          <t>'+0.71%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>117</v>
       </c>
       <c r="F12" t="n">
-        <v>489</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>1654</v>
+        <v>362</v>
       </c>
       <c r="H12" t="n">
-        <v>50.15</v>
+        <v>26.63</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,60 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1840000</v>
+        <v>8470</v>
       </c>
       <c r="K12" t="n">
-        <v>1899000</v>
+        <v>8510</v>
       </c>
       <c r="L12" t="n">
-        <v>1900000</v>
+        <v>8870</v>
       </c>
       <c r="M12" t="n">
-        <v>1836000</v>
+        <v>8470</v>
       </c>
       <c r="N12" t="n">
-        <v>50.17</v>
+        <v>26.58</v>
       </c>
       <c r="O12" t="n">
-        <v>3995123503500</v>
+        <v>25165285855</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q12" t="n">
-        <v>333000</v>
+        <v>8120</v>
       </c>
       <c r="R12" t="n">
-        <v>-289000</v>
+        <v>275000</v>
       </c>
       <c r="S12" t="n">
-        <v>78000</v>
+        <v>-45000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정부 정책 및 정치적 상황으로 인한 주가 하락에 대한 불만 표출. 해외 증시 비교 언급.</t>
+          <t>LG디스플레이의 실적 개선 및 주가 상승 전망이 제기됨. 허수매도 및 주가 조작 의혹과 관련된 부정적 의견도 존재함.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정부정책', 'ADR', '레버리지']</t>
+          <t>['LG디스플레이', '유리기판', 'OLED']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1579,27 +1579,27 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31550</v>
+        <v>31600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.48%</t>
+          <t>'+0.64%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F13" t="n">
         <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H13" t="n">
-        <v>52.8</v>
+        <v>52.79</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>25.75</v>
       </c>
       <c r="O13" t="n">
-        <v>97972760250</v>
+        <v>101611474300</v>
       </c>
       <c r="P13" t="n">
         <v>32100</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8480</v>
+        <v>1848500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.46%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>115</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>486</v>
       </c>
       <c r="G14" t="n">
-        <v>356</v>
+        <v>1697</v>
       </c>
       <c r="H14" t="n">
-        <v>26.63</v>
+        <v>50.15</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8470</v>
+        <v>1840000</v>
       </c>
       <c r="K14" t="n">
-        <v>8510</v>
+        <v>1899000</v>
       </c>
       <c r="L14" t="n">
-        <v>8870</v>
+        <v>1900000</v>
       </c>
       <c r="M14" t="n">
-        <v>8470</v>
+        <v>1836000</v>
       </c>
       <c r="N14" t="n">
-        <v>26.58</v>
+        <v>50.17</v>
       </c>
       <c r="O14" t="n">
-        <v>24751574210</v>
+        <v>4107070109500</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>8120</v>
+        <v>333000</v>
       </c>
       <c r="R14" t="n">
-        <v>275000</v>
+        <v>-289000</v>
       </c>
       <c r="S14" t="n">
-        <v>-45000</v>
+        <v>78000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>LG디스플레이의 실적 개선 및 주가 상승 전망이 제기됨. 허수매도 및 주가 조작 의혹과 관련된 부정적 의견도 존재함.</t>
+          <t>국내 증시 신뢰도 저하 및 정부 정책 비판 속 SK하이닉스 주가 부진에 대한 불만 토로. ADR 상승과 달리 국내 주가 하락.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['LG디스플레이', '유리기판', 'OLED']</t>
+          <t>['국장', 'ADR', '자사주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
         <v>-0.35</v>
       </c>
       <c r="E15" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F15" t="n">
         <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="H15" t="n">
         <v>0.61</v>
@@ -1806,7 +1806,7 @@
         <v>0.96</v>
       </c>
       <c r="O15" t="n">
-        <v>67531088702</v>
+        <v>67735364492</v>
       </c>
       <c r="P15" t="n">
         <v>6300</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30700</v>
+        <v>30550</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'-1.61%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.21</v>
       </c>
       <c r="E16" t="n">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F16" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G16" t="n">
-        <v>2065</v>
+        <v>2092</v>
       </c>
       <c r="H16" t="n">
         <v>16.63</v>
@@ -1898,7 +1898,7 @@
         <v>16.42</v>
       </c>
       <c r="O16" t="n">
-        <v>11002277325</v>
+        <v>11345654850</v>
       </c>
       <c r="P16" t="n">
         <v>69200</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17530</v>
+        <v>17500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.57%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F17" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G17" t="n">
-        <v>839</v>
+        <v>882</v>
       </c>
       <c r="H17" t="n">
         <v>5.46</v>
@@ -1990,7 +1990,7 @@
         <v>6.22</v>
       </c>
       <c r="O17" t="n">
-        <v>134871802100</v>
+        <v>137028368240</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>추석 전 2만원 돌파 기대감과 함께 쇼티지 및 급등 가능성이 언급됨. 주포의 움직임 및 단타 세력에 대한 의견이 존재함.</t>
+          <t>명절 전 상승 기대감 속 2만원 돌파 시도 및 주포 활동 언급. 단타 세력의 빠른 이탈 촉구.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대한광통신', '광통신', '쇼티지']</t>
+          <t>['코스닥', '주포', '단타']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31050</v>
+        <v>30950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-2.06%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
         <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H18" t="n">
         <v>11.7</v>
@@ -2082,7 +2082,7 @@
         <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>76554993650</v>
+        <v>77280662125</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22950</v>
+        <v>49000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.18%</t>
+          <t>'-4.30%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F19" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G19" t="n">
-        <v>128</v>
+        <v>212</v>
       </c>
       <c r="H19" t="n">
-        <v>1.68</v>
+        <v>38.34</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>23950</v>
+        <v>51200</v>
       </c>
       <c r="K19" t="n">
-        <v>24400</v>
+        <v>51600</v>
       </c>
       <c r="L19" t="n">
-        <v>25700</v>
+        <v>51600</v>
       </c>
       <c r="M19" t="n">
-        <v>22700</v>
+        <v>48600</v>
       </c>
       <c r="N19" t="n">
-        <v>1.76</v>
+        <v>38.44</v>
       </c>
       <c r="O19" t="n">
-        <v>72162129775</v>
+        <v>85745837525</v>
       </c>
       <c r="P19" t="n">
-        <v>39350</v>
+        <v>67300</v>
       </c>
       <c r="Q19" t="n">
-        <v>8200</v>
+        <v>23150</v>
       </c>
       <c r="R19" t="n">
-        <v>-53000</v>
+        <v>-327000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>타임지 선정 헬스테크 기업 언급, 저조한 거래량 속 상승 기대감 있으나 매도세 관찰됨.</t>
+          <t>삼성 E&amp;A의 주가 하락에 대한 불만 표현. 20일선 지지 실패 및 6개월 보유 기간에 대한 회의감.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '거래량']</t>
+          <t>['20일선', '주가 하락', 'MSCI']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48850</v>
+        <v>22750</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-5.01%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="F20" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>210</v>
+        <v>134</v>
       </c>
       <c r="H20" t="n">
-        <v>38.34</v>
+        <v>1.68</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>51200</v>
+        <v>23950</v>
       </c>
       <c r="K20" t="n">
-        <v>51600</v>
+        <v>24400</v>
       </c>
       <c r="L20" t="n">
-        <v>51600</v>
+        <v>25700</v>
       </c>
       <c r="M20" t="n">
-        <v>48600</v>
+        <v>22700</v>
       </c>
       <c r="N20" t="n">
-        <v>38.44</v>
+        <v>1.76</v>
       </c>
       <c r="O20" t="n">
-        <v>80992673050</v>
+        <v>72383751275</v>
       </c>
       <c r="P20" t="n">
-        <v>67300</v>
+        <v>39350</v>
       </c>
       <c r="Q20" t="n">
-        <v>23150</v>
+        <v>8200</v>
       </c>
       <c r="R20" t="n">
-        <v>-327000</v>
+        <v>-53000</v>
       </c>
       <c r="S20" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>삼성 E&amp;A의 주가 하락에 대한 불만 표현. 20일선 지지 실패 및 6개월 보유 기간에 대한 회의감.</t>
+          <t>타임지 선정 헬스테크 기업 언급, 저조한 거래량 속 상승 기대감 있으나 매도세 관찰됨.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['20일선', '주가 하락', 'MSCI']</t>
+          <t>['헬스테크', '타임지', '거래량']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>81350</v>
+        <v>81200</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.95%</t>
+          <t>'-6.13%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="F21" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G21" t="n">
-        <v>1902</v>
+        <v>1923</v>
       </c>
       <c r="H21" t="n">
         <v>23.03</v>
@@ -2358,7 +2358,7 @@
         <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>284294294250</v>
+        <v>291815209850</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국형 원전 수주 호재 언급 있으나, 주가 하락에 대한 불만과 정치적 비판이 주를 이룸.</t>
+          <t>원전 관련 긍정적 뉴스에도 불구하고 매도 물량 출회 및 차트 붕괴에 대한 부정적 전망. 외인 숏 포지션 의심.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '주가조작']</t>
+          <t>['원전', 'SMR', '차트']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17420</v>
+        <v>17430</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.34%</t>
+          <t>'-7.29%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.09</v>
       </c>
       <c r="E22" t="n">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="F22" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G22" t="n">
-        <v>1060</v>
+        <v>1096</v>
       </c>
       <c r="H22" t="n">
         <v>10.38</v>
@@ -2450,7 +2450,7 @@
         <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>140394489465</v>
+        <v>141604157755</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2516,7 +2516,7 @@
         <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H23" t="n">
         <v>1.4</v>
@@ -2536,13 +2536,13 @@
         <v>3480</v>
       </c>
       <c r="M23" t="n">
-        <v>2625</v>
+        <v>2610</v>
       </c>
       <c r="N23" t="n">
         <v>0.48</v>
       </c>
       <c r="O23" t="n">
-        <v>22717509617</v>
+        <v>22820897982</v>
       </c>
       <c r="P23" t="n">
         <v>4760</v>

--- a/data/trending_integrated_20260923_14.xlsx
+++ b/data/trending_integrated_20260923_14.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4035</v>
+        <v>4105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.72%</t>
+          <t>'+23.83%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>41944211165</v>
+        <v>42670930162</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -619,7 +619,7 @@
         <v>1809</v>
       </c>
       <c r="R2" t="n">
-        <v>-3000</v>
+        <v>20000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1902</v>
+        <v>1964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.65%</t>
+          <t>'+22.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.39</v>
       </c>
       <c r="E3" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
         <v>138</v>
@@ -702,7 +702,7 @@
         <v>1.41</v>
       </c>
       <c r="O3" t="n">
-        <v>56497031014</v>
+        <v>58296130775</v>
       </c>
       <c r="P3" t="n">
         <v>2465</v>
@@ -711,7 +711,7 @@
         <v>865</v>
       </c>
       <c r="R3" t="n">
-        <v>-358000</v>
+        <v>-400000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17760</v>
+        <v>17900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.43%</t>
+          <t>'+15.34%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G4" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="H4" t="n">
         <v>0.6</v>
@@ -794,7 +794,7 @@
         <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>93406078445</v>
+        <v>94595391950</v>
       </c>
       <c r="P4" t="n">
         <v>34650</v>
@@ -803,10 +803,10 @@
         <v>6980</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14660</v>
+        <v>14470</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.51%</t>
+          <t>'+11.31%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9</v>
+        <v>0.42</v>
       </c>
       <c r="E5" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="H5" t="n">
-        <v>1.89</v>
+        <v>0.86</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13030</v>
+        <v>13000</v>
       </c>
       <c r="K5" t="n">
-        <v>12850</v>
+        <v>12870</v>
       </c>
       <c r="L5" t="n">
-        <v>16420</v>
+        <v>15900</v>
       </c>
       <c r="M5" t="n">
-        <v>12660</v>
+        <v>12650</v>
       </c>
       <c r="N5" t="n">
-        <v>2.79</v>
+        <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>119570389805</v>
+        <v>165543564370</v>
       </c>
       <c r="P5" t="n">
-        <v>64600</v>
+        <v>25700</v>
       </c>
       <c r="Q5" t="n">
-        <v>7520</v>
+        <v>4600</v>
       </c>
       <c r="R5" t="n">
-        <v>2000</v>
+        <v>100000</v>
       </c>
       <c r="S5" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>초소형위성 국방과제 주관 등 사업 모멘텀에 대한 기대감과 함께 주가 하락 및 투경 관련 우려가 공존함.</t>
+          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['나라스페이스', '초소형위성', '우주항공']</t>
+          <t>['2차상승', '단기과열', '명절효과']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>478340</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14440</v>
+        <v>14430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+11.08%</t>
+          <t>'+10.74%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.42</v>
+        <v>-0.9</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H6" t="n">
-        <v>0.86</v>
+        <v>1.89</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13000</v>
+        <v>13030</v>
       </c>
       <c r="K6" t="n">
-        <v>12870</v>
+        <v>12850</v>
       </c>
       <c r="L6" t="n">
-        <v>15900</v>
+        <v>16420</v>
       </c>
       <c r="M6" t="n">
-        <v>12650</v>
+        <v>12660</v>
       </c>
       <c r="N6" t="n">
-        <v>0.44</v>
+        <v>2.79</v>
       </c>
       <c r="O6" t="n">
-        <v>164611551915</v>
+        <v>122109152945</v>
       </c>
       <c r="P6" t="n">
-        <v>25700</v>
+        <v>64600</v>
       </c>
       <c r="Q6" t="n">
-        <v>4600</v>
+        <v>7520</v>
       </c>
       <c r="R6" t="n">
-        <v>84000</v>
+        <v>-11000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-125000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2차 상승 기대감 및 단기 과열 지정 가능성 언급. 명절 전 상승 후 하락 가능성 제기.</t>
+          <t>초소형위성 국방과제 주관 등 사업 모멘텀에 대한 기대감과 함께 주가 하락 및 투경 관련 우려가 공존함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['2차상승', '단기과열', '명절효과']</t>
+          <t>['나라스페이스', '초소형위성', '우주항공']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>478340</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18170</v>
+        <v>18280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.85%</t>
+          <t>'+10.52%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F7" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G7" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H7" t="n">
         <v>0.62</v>
@@ -1070,7 +1070,7 @@
         <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>302924285370</v>
+        <v>306378197175</v>
       </c>
       <c r="P7" t="n">
         <v>30550</v>
@@ -1079,7 +1079,7 @@
         <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>-77000</v>
+        <v>-45000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>219750</v>
+        <v>219500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.90%</t>
+          <t>'+3.78%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="H8" t="n">
         <v>75.51000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>75.5</v>
       </c>
       <c r="O8" t="n">
-        <v>879746824500</v>
+        <v>910173031500</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1171,10 +1171,10 @@
         <v>65000</v>
       </c>
       <c r="R8" t="n">
-        <v>605000</v>
+        <v>715000</v>
       </c>
       <c r="S8" t="n">
-        <v>-57000</v>
+        <v>-52000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7820</v>
+        <v>7860</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.76%</t>
+          <t>'+3.29%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F9" t="n">
         <v>57</v>
       </c>
       <c r="G9" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H9" t="n">
         <v>1.9</v>
@@ -1254,7 +1254,7 @@
         <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>89738678160</v>
+        <v>89952866095</v>
       </c>
       <c r="P9" t="n">
         <v>16200</v>
@@ -1263,10 +1263,10 @@
         <v>1206</v>
       </c>
       <c r="R9" t="n">
-        <v>-26000</v>
+        <v>-35000</v>
       </c>
       <c r="S9" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>283750</v>
+        <v>284250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.80%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G10" t="n">
-        <v>1919</v>
+        <v>1880</v>
       </c>
       <c r="H10" t="n">
         <v>46.55</v>
@@ -1346,7 +1346,7 @@
         <v>46.56</v>
       </c>
       <c r="O10" t="n">
-        <v>3770998262250</v>
+        <v>3899166102250</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1355,23 +1355,23 @@
         <v>82400</v>
       </c>
       <c r="R10" t="n">
-        <v>1963000</v>
+        <v>1926000</v>
       </c>
       <c r="S10" t="n">
-        <v>599000</v>
+        <v>790000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 언급과 개인적인 주가 예상만 난무하며, 구체적인 사실 기반 분석 부재.</t>
+          <t>정치적 발언과 함께 특정 가격 돌파 기대감이 있으나, 명확한 근거 제시 부족.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['주가', '전망', '돌파']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13930</v>
+        <v>13900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.43%</t>
+          <t>'+2.21%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="H11" t="n">
         <v>9.609999999999999</v>
@@ -1438,7 +1438,7 @@
         <v>9.77</v>
       </c>
       <c r="O11" t="n">
-        <v>98430672720</v>
+        <v>98948378975</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1447,10 +1447,10 @@
         <v>5780</v>
       </c>
       <c r="R11" t="n">
-        <v>211000</v>
+        <v>246000</v>
       </c>
       <c r="S11" t="n">
-        <v>-397000</v>
+        <v>-494000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8530</v>
+        <v>31800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.71%</t>
+          <t>'+1.27%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0.62</v>
       </c>
       <c r="E12" t="n">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>362</v>
+        <v>153</v>
       </c>
       <c r="H12" t="n">
-        <v>26.63</v>
+        <v>52.82</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8470</v>
+        <v>31400</v>
       </c>
       <c r="K12" t="n">
-        <v>8510</v>
+        <v>31500</v>
       </c>
       <c r="L12" t="n">
-        <v>8870</v>
+        <v>32100</v>
       </c>
       <c r="M12" t="n">
-        <v>8470</v>
+        <v>31100</v>
       </c>
       <c r="N12" t="n">
-        <v>26.58</v>
+        <v>25.75</v>
       </c>
       <c r="O12" t="n">
-        <v>25165285855</v>
+        <v>110493119725</v>
       </c>
       <c r="P12" t="n">
-        <v>17950</v>
+        <v>32100</v>
       </c>
       <c r="Q12" t="n">
-        <v>8120</v>
+        <v>21000</v>
       </c>
       <c r="R12" t="n">
-        <v>275000</v>
+        <v>-81000</v>
       </c>
       <c r="S12" t="n">
-        <v>-45000</v>
+        <v>219000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>LG디스플레이의 실적 개선 및 주가 상승 전망이 제기됨. 허수매도 및 주가 조작 의혹과 관련된 부정적 의견도 존재함.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['LG디스플레이', '유리기판', 'OLED']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31600</v>
+        <v>8500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.64%</t>
+          <t>'+0.35%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.62</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>152</v>
+        <v>366</v>
       </c>
       <c r="H13" t="n">
-        <v>52.79</v>
+        <v>26.63</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>31400</v>
+        <v>8470</v>
       </c>
       <c r="K13" t="n">
-        <v>31500</v>
+        <v>8510</v>
       </c>
       <c r="L13" t="n">
-        <v>32100</v>
+        <v>8870</v>
       </c>
       <c r="M13" t="n">
-        <v>31100</v>
+        <v>8470</v>
       </c>
       <c r="N13" t="n">
-        <v>25.75</v>
+        <v>26.58</v>
       </c>
       <c r="O13" t="n">
-        <v>101611474300</v>
+        <v>25865682655</v>
       </c>
       <c r="P13" t="n">
-        <v>32100</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>21000</v>
+        <v>8120</v>
       </c>
       <c r="R13" t="n">
-        <v>-37000</v>
+        <v>276000</v>
       </c>
       <c r="S13" t="n">
-        <v>174000</v>
+        <v>-68000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
+          <t>LG디스플레이의 실적 개선 및 주가 상승 전망이 제기됨. 허수매도 및 주가 조작 의혹과 관련된 부정적 의견도 존재함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '인천공항']</t>
+          <t>['LG디스플레이', '유리기판', 'OLED']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1848500</v>
+        <v>1846000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.46%</t>
+          <t>'+0.33%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G14" t="n">
-        <v>1697</v>
+        <v>1688</v>
       </c>
       <c r="H14" t="n">
         <v>50.15</v>
@@ -1714,7 +1714,7 @@
         <v>50.17</v>
       </c>
       <c r="O14" t="n">
-        <v>4107070109500</v>
+        <v>4181233578000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1723,14 +1723,14 @@
         <v>333000</v>
       </c>
       <c r="R14" t="n">
-        <v>-289000</v>
+        <v>-536000</v>
       </c>
       <c r="S14" t="n">
-        <v>78000</v>
+        <v>91000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국내 증시 신뢰도 저하 및 정부 정책 비판 속 SK하이닉스 주가 부진에 대한 불만 토로. ADR 상승과 달리 국내 주가 하락.</t>
+          <t>국내 증시 전반의 신뢰도 하락 속에서 반도체 업황 개선 기대에도 불구하고 주가 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['국장', 'ADR', '자사주']</t>
+          <t>['반도체', '국내 증시', '주가 관리']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3705</v>
+        <v>3690</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.54%</t>
+          <t>'-0.94%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.35</v>
       </c>
       <c r="E15" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="H15" t="n">
         <v>0.61</v>
@@ -1806,7 +1806,7 @@
         <v>0.96</v>
       </c>
       <c r="O15" t="n">
-        <v>67735364492</v>
+        <v>67912206892</v>
       </c>
       <c r="P15" t="n">
         <v>6300</v>
@@ -1815,14 +1815,14 @@
         <v>1738</v>
       </c>
       <c r="R15" t="n">
-        <v>-191000</v>
+        <v>-176000</v>
       </c>
       <c r="S15" t="n">
         <v>-5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>급격한 주가 하락 및 물량 떠넘기기에 대한 불만이 제기됨. 상폐 가능성 및 단타 위주의 거래에 대한 부정적 인식이 나타남.</t>
+          <t>급격한 하락과 반복적인 음봉으로 인한 투자자들의 불안감 증폭 및 투기성 거래에 대한 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['급락', '음봉', '투기']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30550</v>
+        <v>17480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.61%</t>
+          <t>'-1.85%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.21</v>
+        <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>326</v>
+        <v>140</v>
       </c>
       <c r="F16" t="n">
-        <v>198</v>
+        <v>83</v>
       </c>
       <c r="G16" t="n">
-        <v>2092</v>
+        <v>899</v>
       </c>
       <c r="H16" t="n">
-        <v>16.63</v>
+        <v>5.46</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>31050</v>
+        <v>17810</v>
       </c>
       <c r="K16" t="n">
-        <v>31300</v>
+        <v>17950</v>
       </c>
       <c r="L16" t="n">
-        <v>31550</v>
+        <v>18180</v>
       </c>
       <c r="M16" t="n">
-        <v>30050</v>
+        <v>17410</v>
       </c>
       <c r="N16" t="n">
-        <v>16.42</v>
+        <v>6.22</v>
       </c>
       <c r="O16" t="n">
-        <v>11345654850</v>
+        <v>138714707425</v>
       </c>
       <c r="P16" t="n">
-        <v>69200</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>24150</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-88000</v>
+        <v>-273000</v>
       </c>
       <c r="S16" t="n">
-        <v>-2000</v>
+        <v>1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 릴라이테라퓨틱스 상승 및 FDA 승인 기대감, 간암/담관암 결과 발표 대기 중. HLB 담관암 신약 FDA 허가 임박 소식.</t>
+          <t>명절 전 상승 기대감 속 2만원 돌파 시도 및 주포 활동 언급. 단타 세력의 빠른 이탈 촉구.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['FDA', '릴라이테라퓨틱스', '신약']</t>
+          <t>['코스닥', '주포', '단타']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,191 +1936,191 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17500</v>
+        <v>30950</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-2.06%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.76</v>
+        <v>0.4</v>
       </c>
       <c r="E17" t="n">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="F17" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>882</v>
+        <v>130</v>
       </c>
       <c r="H17" t="n">
-        <v>5.46</v>
+        <v>11.7</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17810</v>
+        <v>31600</v>
       </c>
       <c r="K17" t="n">
-        <v>17950</v>
+        <v>32150</v>
       </c>
       <c r="L17" t="n">
-        <v>18180</v>
+        <v>32200</v>
       </c>
       <c r="M17" t="n">
-        <v>17410</v>
+        <v>30550</v>
       </c>
       <c r="N17" t="n">
-        <v>6.22</v>
+        <v>11.3</v>
       </c>
       <c r="O17" t="n">
-        <v>137028368240</v>
+        <v>77963747450</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>75900</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>15000</v>
       </c>
       <c r="R17" t="n">
-        <v>-215000</v>
+        <v>-728000</v>
       </c>
       <c r="S17" t="n">
-        <v>1000</v>
+        <v>-39000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>명절 전 상승 기대감 속 2만원 돌파 시도 및 주포 활동 언급. 단타 세력의 빠른 이탈 촉구.</t>
+          <t>구리 선물가 상승과 함께 주가 상승 기대감, 타 종목과의 비교 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['코스닥', '주포', '단타']</t>
+          <t>['구리', '텍사스', '가온전선']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30950</v>
+        <v>30400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.06%</t>
+          <t>'-2.09%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.21</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>332</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="G18" t="n">
-        <v>129</v>
+        <v>2098</v>
       </c>
       <c r="H18" t="n">
-        <v>11.7</v>
+        <v>16.63</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>31600</v>
+        <v>31050</v>
       </c>
       <c r="K18" t="n">
-        <v>32150</v>
+        <v>31300</v>
       </c>
       <c r="L18" t="n">
-        <v>32200</v>
+        <v>31550</v>
       </c>
       <c r="M18" t="n">
-        <v>30550</v>
+        <v>30050</v>
       </c>
       <c r="N18" t="n">
-        <v>11.3</v>
+        <v>16.42</v>
       </c>
       <c r="O18" t="n">
-        <v>77280662125</v>
+        <v>11917991250</v>
       </c>
       <c r="P18" t="n">
-        <v>75900</v>
+        <v>69200</v>
       </c>
       <c r="Q18" t="n">
-        <v>15000</v>
+        <v>24150</v>
       </c>
       <c r="R18" t="n">
-        <v>-681000</v>
+        <v>-111000</v>
       </c>
       <c r="S18" t="n">
-        <v>-39000</v>
+        <v>-3000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>구리 선물가 상승과 함께 주가 상승 기대감, 타 종목과의 비교 언급.</t>
+          <t>미국 릴리사 항암제 관련 긍정적인 소식과 함께 승인 기대감이 높으나, 실제 결과 발표 지연.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['구리', '텍사스', '가온전선']</t>
+          <t>['항암제', '승인', '릴리사']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>49000</v>
+        <v>48900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.30%</t>
+          <t>'-4.49%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>72</v>
       </c>
       <c r="G19" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="H19" t="n">
         <v>38.34</v>
@@ -2174,7 +2174,7 @@
         <v>38.44</v>
       </c>
       <c r="O19" t="n">
-        <v>85745837525</v>
+        <v>87345541425</v>
       </c>
       <c r="P19" t="n">
         <v>67300</v>
@@ -2183,10 +2183,10 @@
         <v>23150</v>
       </c>
       <c r="R19" t="n">
-        <v>-327000</v>
+        <v>-432000</v>
       </c>
       <c r="S19" t="n">
-        <v>-30000</v>
+        <v>-6000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22750</v>
+        <v>22800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.01%</t>
+          <t>'-4.80%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.08</v>
       </c>
       <c r="E20" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
         <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H20" t="n">
         <v>1.68</v>
@@ -2266,7 +2266,7 @@
         <v>1.76</v>
       </c>
       <c r="O20" t="n">
-        <v>72383751275</v>
+        <v>72805518550</v>
       </c>
       <c r="P20" t="n">
         <v>39350</v>
@@ -2275,7 +2275,7 @@
         <v>8200</v>
       </c>
       <c r="R20" t="n">
-        <v>-53000</v>
+        <v>-50000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="F21" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G21" t="n">
-        <v>1923</v>
+        <v>1950</v>
       </c>
       <c r="H21" t="n">
         <v>23.03</v>
@@ -2358,7 +2358,7 @@
         <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>291815209850</v>
+        <v>296459974050</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2367,23 +2367,23 @@
         <v>57000</v>
       </c>
       <c r="R21" t="n">
-        <v>-1068000</v>
+        <v>-1175000</v>
       </c>
       <c r="S21" t="n">
-        <v>-190000</v>
+        <v>-226000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 관련 긍정적 뉴스에도 불구하고 매도 물량 출회 및 차트 붕괴에 대한 부정적 전망. 외인 숏 포지션 의심.</t>
+          <t>미국 원전 수출 관련 긍정적 뉴스에도 불구하고, 차트 붕괴 및 재료 소멸 우려로 부정적 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '차트']</t>
+          <t>['원전', '수출', '재료 소멸']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17430</v>
+        <v>17370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.29%</t>
+          <t>'-7.61%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.09</v>
       </c>
       <c r="E22" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F22" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G22" t="n">
-        <v>1096</v>
+        <v>1110</v>
       </c>
       <c r="H22" t="n">
         <v>10.38</v>
@@ -2450,7 +2450,7 @@
         <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>141604157755</v>
+        <v>144582252580</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2459,10 +2459,10 @@
         <v>3320</v>
       </c>
       <c r="R22" t="n">
-        <v>-2242000</v>
+        <v>-2290000</v>
       </c>
       <c r="S22" t="n">
-        <v>-454000</v>
+        <v>-506000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2635</v>
+        <v>2665</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.67%</t>
+          <t>'-7.63%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.92</v>
       </c>
       <c r="E23" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F23" t="n">
         <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H23" t="n">
         <v>1.4</v>
@@ -2542,7 +2542,7 @@
         <v>0.48</v>
       </c>
       <c r="O23" t="n">
-        <v>22820897982</v>
+        <v>22875360847</v>
       </c>
       <c r="P23" t="n">
         <v>4760</v>
@@ -2551,7 +2551,7 @@
         <v>973</v>
       </c>
       <c r="R23" t="n">
-        <v>-199000</v>
+        <v>-212000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260923_14.xlsx
+++ b/data/trending_integrated_20260923_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4105</v>
+        <v>4160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.83%</t>
+          <t>'+25.49%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>42670930162</v>
+        <v>45114373812</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1964</v>
+        <v>1954</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.52%</t>
+          <t>'+21.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.39</v>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H3" t="n">
         <v>1.02</v>
@@ -702,7 +702,7 @@
         <v>1.41</v>
       </c>
       <c r="O3" t="n">
-        <v>58296130775</v>
+        <v>59845116275</v>
       </c>
       <c r="P3" t="n">
         <v>2465</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17900</v>
+        <v>18670</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.34%</t>
+          <t>'+20.30%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.5</v>
       </c>
       <c r="E4" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="H4" t="n">
         <v>0.6</v>
@@ -794,7 +794,7 @@
         <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>94595391950</v>
+        <v>100466300255</v>
       </c>
       <c r="P4" t="n">
         <v>34650</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>스페이스X 우주 임무 선정 및 인도발 수주 등 강력한 호재 기반으로 한 레메디의 급등세 전망. 기술력 검증 및 시장 확대 기대.</t>
+          <t>NASA 및 스페이스X 선정과 11조원 시장 도전 등 구체적인 사업 내용과 규모가 언급되며 높은 상승 기대감을 형성함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['스페이스X', '엑스레이', '수주']</t>
+          <t>['스페이스X', 'X-ray']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14470</v>
+        <v>14420</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.31%</t>
+          <t>'+10.92%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.42</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
         <v>113</v>
@@ -886,7 +886,7 @@
         <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>165543564370</v>
+        <v>166183838830</v>
       </c>
       <c r="P5" t="n">
         <v>25700</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14430</v>
+        <v>18285</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.74%</t>
+          <t>'+10.55%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.9</v>
+        <v>-0.15</v>
       </c>
       <c r="E6" t="n">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>138</v>
       </c>
       <c r="G6" t="n">
-        <v>112</v>
+        <v>313</v>
       </c>
       <c r="H6" t="n">
-        <v>1.89</v>
+        <v>0.62</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13030</v>
+        <v>16540</v>
       </c>
       <c r="K6" t="n">
-        <v>12850</v>
+        <v>17530</v>
       </c>
       <c r="L6" t="n">
-        <v>16420</v>
+        <v>19950</v>
       </c>
       <c r="M6" t="n">
-        <v>12660</v>
+        <v>17500</v>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>0.77</v>
       </c>
       <c r="O6" t="n">
-        <v>122109152945</v>
+        <v>307686595195</v>
       </c>
       <c r="P6" t="n">
-        <v>64600</v>
+        <v>30550</v>
       </c>
       <c r="Q6" t="n">
-        <v>7520</v>
+        <v>6100</v>
       </c>
       <c r="R6" t="n">
-        <v>-11000</v>
+        <v>-45000</v>
       </c>
       <c r="S6" t="n">
-        <v>-125000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>초소형위성 국방과제 주관 등 사업 모멘텀에 대한 기대감과 함께 주가 하락 및 투경 관련 우려가 공존함.</t>
+          <t>미국 양자 관련주 급등 소식과 함께 국내 양자 보안 테마의 상승 가능성을 언급하며 긍정적인 전망을 보이고 있습니다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['나라스페이스', '초소형위성', '우주항공']</t>
+          <t>['양자', '보안']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>478340</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18280</v>
+        <v>14180</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.52%</t>
+          <t>'+8.83%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.15</v>
+        <v>-0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>187</v>
+        <v>122</v>
       </c>
       <c r="F7" t="n">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
-        <v>309</v>
+        <v>119</v>
       </c>
       <c r="H7" t="n">
-        <v>0.62</v>
+        <v>1.89</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16540</v>
+        <v>13030</v>
       </c>
       <c r="K7" t="n">
-        <v>17530</v>
+        <v>12850</v>
       </c>
       <c r="L7" t="n">
-        <v>19950</v>
+        <v>16420</v>
       </c>
       <c r="M7" t="n">
-        <v>17500</v>
+        <v>12660</v>
       </c>
       <c r="N7" t="n">
-        <v>0.77</v>
+        <v>2.79</v>
       </c>
       <c r="O7" t="n">
-        <v>306378197175</v>
+        <v>123734270680</v>
       </c>
       <c r="P7" t="n">
-        <v>30550</v>
+        <v>64600</v>
       </c>
       <c r="Q7" t="n">
-        <v>6100</v>
+        <v>7520</v>
       </c>
       <c r="R7" t="n">
-        <v>-45000</v>
+        <v>-11000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-125000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등 소식과 함께 국내 양자 보안 테마의 상승 가능성을 언급하며 긍정적인 전망을 보이고 있습니다.</t>
+          <t>초소형 위성 관련 긍정적인 공시에도 불구하고, 주가 변동성에 대한 불안감과 단기적인 시세 차익에 대한 기대가 혼재함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자', '보안']</t>
+          <t>['초소형 위성', '국방 과제']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,169 +1108,169 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>478340</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>219500</v>
+        <v>7910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.78%</t>
+          <t>'+3.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>-0.42</v>
       </c>
       <c r="E8" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="G8" t="n">
-        <v>458</v>
+        <v>352</v>
       </c>
       <c r="H8" t="n">
-        <v>75.51000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>211500</v>
+        <v>7610</v>
       </c>
       <c r="K8" t="n">
-        <v>217000</v>
+        <v>7850</v>
       </c>
       <c r="L8" t="n">
-        <v>220000</v>
+        <v>8720</v>
       </c>
       <c r="M8" t="n">
-        <v>216500</v>
+        <v>7730</v>
       </c>
       <c r="N8" t="n">
-        <v>75.5</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>910173031500</v>
+        <v>90374138295</v>
       </c>
       <c r="P8" t="n">
-        <v>243500</v>
+        <v>16200</v>
       </c>
       <c r="Q8" t="n">
-        <v>65000</v>
+        <v>1206</v>
       </c>
       <c r="R8" t="n">
-        <v>715000</v>
+        <v>-35000</v>
       </c>
       <c r="S8" t="n">
-        <v>-52000</v>
+        <v>2000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>평생 보유 및 수천만원대 배당금 수령에 대한 기대감이 높음. 우선주 소각 이슈와 자사주 관련 언급이 있음.</t>
+          <t>대표의 계단식 하락 유도 및 지독한 매도에 대한 불만이 제기됨. 실체 있는 기업이라는 긍정적 언급과 과열 우려가 공존함.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['우선주', '배당금', '자사주']</t>
+          <t>['우리로', '양자', '빛샘']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7860</v>
+        <v>219500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.29%</t>
+          <t>'+3.78%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.42</v>
+        <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="G9" t="n">
-        <v>345</v>
+        <v>469</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7610</v>
+        <v>211500</v>
       </c>
       <c r="K9" t="n">
-        <v>7850</v>
+        <v>217000</v>
       </c>
       <c r="L9" t="n">
-        <v>8720</v>
+        <v>220000</v>
       </c>
       <c r="M9" t="n">
-        <v>7730</v>
+        <v>216500</v>
       </c>
       <c r="N9" t="n">
-        <v>2.32</v>
+        <v>75.5</v>
       </c>
       <c r="O9" t="n">
-        <v>89952866095</v>
+        <v>942389982500</v>
       </c>
       <c r="P9" t="n">
-        <v>16200</v>
+        <v>243500</v>
       </c>
       <c r="Q9" t="n">
-        <v>1206</v>
+        <v>65000</v>
       </c>
       <c r="R9" t="n">
-        <v>-35000</v>
+        <v>715000</v>
       </c>
       <c r="S9" t="n">
-        <v>2000</v>
+        <v>-52000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대표의 계단식 하락 유도 및 지독한 매도에 대한 불만이 제기됨. 실체 있는 기업이라는 긍정적 언급과 과열 우려가 공존함.</t>
+          <t>평생 보유 및 수천만원대 배당금 수령에 대한 기대감이 높음. 우선주 소각 이슈와 자사주 관련 언급이 있음.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['우리로', '양자', '빛샘']</t>
+          <t>['우선주', '배당금', '자사주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>284250</v>
+        <v>284500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.80%</t>
+          <t>'+2.89%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="G10" t="n">
-        <v>1880</v>
+        <v>1824</v>
       </c>
       <c r="H10" t="n">
         <v>46.55</v>
@@ -1346,7 +1346,7 @@
         <v>46.56</v>
       </c>
       <c r="O10" t="n">
-        <v>3899166102250</v>
+        <v>4010591889000</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 발언과 함께 특정 가격 돌파 기대감이 있으나, 명확한 근거 제시 부족.</t>
+          <t>개인 투자자들의 긍정적인 기대감 속에서 주가 상승 전망이 있으나, 감정적인 표현과 정치적 언급이 다수 포함됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가', '전망', '돌파']</t>
+          <t>['주가 전망', '개미 투자']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13900</v>
+        <v>13880</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.21%</t>
+          <t>'+2.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
         <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H11" t="n">
         <v>9.609999999999999</v>
@@ -1438,7 +1438,7 @@
         <v>9.77</v>
       </c>
       <c r="O11" t="n">
-        <v>98948378975</v>
+        <v>99703243065</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31800</v>
+        <v>31750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.27%</t>
+          <t>'+1.11%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.62</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="H12" t="n">
         <v>52.82</v>
@@ -1530,7 +1530,7 @@
         <v>25.75</v>
       </c>
       <c r="O12" t="n">
-        <v>110493119725</v>
+        <v>112491441900</v>
       </c>
       <c r="P12" t="n">
         <v>32100</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8500</v>
+        <v>1845000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.35%</t>
+          <t>'+0.27%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>118</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>482</v>
       </c>
       <c r="G13" t="n">
-        <v>366</v>
+        <v>1643</v>
       </c>
       <c r="H13" t="n">
-        <v>26.63</v>
+        <v>50.15</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8470</v>
+        <v>1840000</v>
       </c>
       <c r="K13" t="n">
-        <v>8510</v>
+        <v>1899000</v>
       </c>
       <c r="L13" t="n">
-        <v>8870</v>
+        <v>1900000</v>
       </c>
       <c r="M13" t="n">
-        <v>8470</v>
+        <v>1836000</v>
       </c>
       <c r="N13" t="n">
-        <v>26.58</v>
+        <v>50.17</v>
       </c>
       <c r="O13" t="n">
-        <v>25865682655</v>
+        <v>4285120691000</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>8120</v>
+        <v>333000</v>
       </c>
       <c r="R13" t="n">
-        <v>276000</v>
+        <v>-536000</v>
       </c>
       <c r="S13" t="n">
-        <v>-68000</v>
+        <v>91000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>LG디스플레이의 실적 개선 및 주가 상승 전망이 제기됨. 허수매도 및 주가 조작 의혹과 관련된 부정적 의견도 존재함.</t>
+          <t>반도체 업황 회복 기대감에도 불구하고, 주가 부진에 대한 불만과 정부 정책 비판 등 부정적인 심리가 지배적임.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['LG디스플레이', '유리기판', 'OLED']</t>
+          <t>['반도체', '주가 관리']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1846000</v>
+        <v>8490</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'+0.24%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>118</v>
       </c>
       <c r="F14" t="n">
-        <v>485</v>
+        <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>1688</v>
+        <v>369</v>
       </c>
       <c r="H14" t="n">
-        <v>50.15</v>
+        <v>26.63</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1840000</v>
+        <v>8470</v>
       </c>
       <c r="K14" t="n">
-        <v>1899000</v>
+        <v>8510</v>
       </c>
       <c r="L14" t="n">
-        <v>1900000</v>
+        <v>8870</v>
       </c>
       <c r="M14" t="n">
-        <v>1836000</v>
+        <v>8470</v>
       </c>
       <c r="N14" t="n">
-        <v>50.17</v>
+        <v>26.58</v>
       </c>
       <c r="O14" t="n">
-        <v>4181233578000</v>
+        <v>26219865670</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>333000</v>
+        <v>8120</v>
       </c>
       <c r="R14" t="n">
-        <v>-536000</v>
+        <v>276000</v>
       </c>
       <c r="S14" t="n">
-        <v>91000</v>
+        <v>-68000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국내 증시 전반의 신뢰도 하락 속에서 반도체 업황 개선 기대에도 불구하고 주가 부진에 대한 불만.</t>
+          <t>LG디스플레이의 실적 개선 및 주가 상승 전망이 제기됨. 허수매도 및 주가 조작 의혹과 관련된 부정적 의견도 존재함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '국내 증시', '주가 관리']</t>
+          <t>['LG디스플레이', '유리기판', 'OLED']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
         <v>-0.35</v>
       </c>
       <c r="E15" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F15" t="n">
         <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="H15" t="n">
         <v>0.61</v>
@@ -1806,7 +1806,7 @@
         <v>0.96</v>
       </c>
       <c r="O15" t="n">
-        <v>67912206892</v>
+        <v>68370687345</v>
       </c>
       <c r="P15" t="n">
         <v>6300</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>급격한 하락과 반복적인 음봉으로 인한 투자자들의 불안감 증폭 및 투기성 거래에 대한 비판.</t>
+          <t>주가 급락에 대한 강한 불만과 함께, 종목 자체에 대한 부정적인 평가 및 투자자 이탈 움직임이 관찰됨.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['급락', '음봉', '투기']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17480</v>
+        <v>17550</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.85%</t>
+          <t>'-1.46%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>83</v>
       </c>
       <c r="G16" t="n">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="H16" t="n">
         <v>5.46</v>
@@ -1898,7 +1898,7 @@
         <v>6.22</v>
       </c>
       <c r="O16" t="n">
-        <v>138714707425</v>
+        <v>139861146475</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1943,254 +1943,254 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30950</v>
+        <v>30500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.06%</t>
+          <t>'-1.77%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.4</v>
+        <v>0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>347</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>209</v>
       </c>
       <c r="G17" t="n">
-        <v>130</v>
+        <v>2150</v>
       </c>
       <c r="H17" t="n">
-        <v>11.7</v>
+        <v>16.63</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>31600</v>
+        <v>31050</v>
       </c>
       <c r="K17" t="n">
-        <v>32150</v>
+        <v>31300</v>
       </c>
       <c r="L17" t="n">
-        <v>32200</v>
+        <v>31550</v>
       </c>
       <c r="M17" t="n">
-        <v>30550</v>
+        <v>30050</v>
       </c>
       <c r="N17" t="n">
-        <v>11.3</v>
+        <v>16.42</v>
       </c>
       <c r="O17" t="n">
-        <v>77963747450</v>
+        <v>12772201700</v>
       </c>
       <c r="P17" t="n">
-        <v>75900</v>
+        <v>69200</v>
       </c>
       <c r="Q17" t="n">
-        <v>15000</v>
+        <v>24150</v>
       </c>
       <c r="R17" t="n">
-        <v>-728000</v>
+        <v>-111000</v>
       </c>
       <c r="S17" t="n">
-        <v>-39000</v>
+        <v>-3000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>구리 선물가 상승과 함께 주가 상승 기대감, 타 종목과의 비교 언급.</t>
+          <t>미국 릴리사 항암제 관련 긍정적인 소식과 함께 승인 기대감이 높으나, 실제 결과 발표 지연.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['구리', '텍사스', '가온전선']</t>
+          <t>['항암제', '승인', '릴리사']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30400</v>
+        <v>30800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.09%</t>
+          <t>'-2.53%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>332</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
-        <v>201</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>2098</v>
+        <v>133</v>
       </c>
       <c r="H18" t="n">
-        <v>16.63</v>
+        <v>11.7</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>31050</v>
+        <v>31600</v>
       </c>
       <c r="K18" t="n">
-        <v>31300</v>
+        <v>32150</v>
       </c>
       <c r="L18" t="n">
-        <v>31550</v>
+        <v>32200</v>
       </c>
       <c r="M18" t="n">
-        <v>30050</v>
+        <v>30550</v>
       </c>
       <c r="N18" t="n">
-        <v>16.42</v>
+        <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>11917991250</v>
+        <v>79158989925</v>
       </c>
       <c r="P18" t="n">
-        <v>69200</v>
+        <v>75900</v>
       </c>
       <c r="Q18" t="n">
-        <v>24150</v>
+        <v>15000</v>
       </c>
       <c r="R18" t="n">
-        <v>-111000</v>
+        <v>-728000</v>
       </c>
       <c r="S18" t="n">
-        <v>-3000</v>
+        <v>-39000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 릴리사 항암제 관련 긍정적인 소식과 함께 승인 기대감이 높으나, 실제 결과 발표 지연.</t>
+          <t>구리 선물가 상승과 함께 주가 상승 기대감, 타 종목과의 비교 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['항암제', '승인', '릴리사']</t>
+          <t>['구리', '텍사스', '가온전선']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>48900</v>
+        <v>23100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.49%</t>
+          <t>'-3.55%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F19" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>219</v>
+        <v>140</v>
       </c>
       <c r="H19" t="n">
-        <v>38.34</v>
+        <v>1.68</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>51200</v>
+        <v>23950</v>
       </c>
       <c r="K19" t="n">
-        <v>51600</v>
+        <v>24400</v>
       </c>
       <c r="L19" t="n">
-        <v>51600</v>
+        <v>25700</v>
       </c>
       <c r="M19" t="n">
-        <v>48600</v>
+        <v>22700</v>
       </c>
       <c r="N19" t="n">
-        <v>38.44</v>
+        <v>1.76</v>
       </c>
       <c r="O19" t="n">
-        <v>87345541425</v>
+        <v>73479175300</v>
       </c>
       <c r="P19" t="n">
-        <v>67300</v>
+        <v>39350</v>
       </c>
       <c r="Q19" t="n">
-        <v>23150</v>
+        <v>8200</v>
       </c>
       <c r="R19" t="n">
-        <v>-432000</v>
+        <v>-50000</v>
       </c>
       <c r="S19" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>삼성 E&amp;A의 주가 하락에 대한 불만 표현. 20일선 지지 실패 및 6개월 보유 기간에 대한 회의감.</t>
+          <t>타임지 선정 헬스테크 기업 언급, 저조한 거래량 속 상승 기대감 있으나 매도세 관찰됨.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['20일선', '주가 하락', 'MSCI']</t>
+          <t>['헬스테크', '타임지', '거래량']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22800</v>
+        <v>48900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.80%</t>
+          <t>'-4.49%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="G20" t="n">
-        <v>138</v>
+        <v>220</v>
       </c>
       <c r="H20" t="n">
-        <v>1.68</v>
+        <v>38.34</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>23950</v>
+        <v>51200</v>
       </c>
       <c r="K20" t="n">
-        <v>24400</v>
+        <v>51600</v>
       </c>
       <c r="L20" t="n">
-        <v>25700</v>
+        <v>51600</v>
       </c>
       <c r="M20" t="n">
-        <v>22700</v>
+        <v>48600</v>
       </c>
       <c r="N20" t="n">
-        <v>1.76</v>
+        <v>38.44</v>
       </c>
       <c r="O20" t="n">
-        <v>72805518550</v>
+        <v>88802086825</v>
       </c>
       <c r="P20" t="n">
-        <v>39350</v>
+        <v>67300</v>
       </c>
       <c r="Q20" t="n">
-        <v>8200</v>
+        <v>23150</v>
       </c>
       <c r="R20" t="n">
-        <v>-50000</v>
+        <v>-432000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>타임지 선정 헬스테크 기업 언급, 저조한 거래량 속 상승 기대감 있으나 매도세 관찰됨.</t>
+          <t>삼성 E&amp;A의 주가 하락에 대한 불만 표현. 20일선 지지 실패 및 6개월 보유 기간에 대한 회의감.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '거래량']</t>
+          <t>['20일선', '주가 하락', 'MSCI']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>81200</v>
+        <v>81000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.13%</t>
+          <t>'-6.36%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="F21" t="n">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="G21" t="n">
-        <v>1950</v>
+        <v>2012</v>
       </c>
       <c r="H21" t="n">
         <v>23.03</v>
@@ -2358,7 +2358,7 @@
         <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>296459974050</v>
+        <v>305321313750</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 원전 수출 관련 긍정적 뉴스에도 불구하고, 차트 붕괴 및 재료 소멸 우려로 부정적 전망.</t>
+          <t>원전 관련 긍정적 뉴스에도 불구하고, 주가 하락에 대한 불안감과 부정적인 전망이 혼재하며 투자자들의 혼란이 감지됨.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '수출', '재료 소멸']</t>
+          <t>['원전', '주가 조작']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17370</v>
+        <v>17380</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.61%</t>
+          <t>'-7.55%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.09</v>
       </c>
       <c r="E22" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F22" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G22" t="n">
-        <v>1110</v>
+        <v>1182</v>
       </c>
       <c r="H22" t="n">
         <v>10.38</v>
@@ -2444,13 +2444,13 @@
         <v>18800</v>
       </c>
       <c r="M22" t="n">
-        <v>17370</v>
+        <v>17360</v>
       </c>
       <c r="N22" t="n">
         <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>144582252580</v>
+        <v>146797698550</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2665</v>
+        <v>2650</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-7.63%</t>
+          <t>'-8.15%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="H23" t="n">
         <v>1.4</v>
@@ -2542,7 +2542,7 @@
         <v>0.48</v>
       </c>
       <c r="O23" t="n">
-        <v>22875360847</v>
+        <v>22908801442</v>
       </c>
       <c r="P23" t="n">
         <v>4760</v>

--- a/data/trending_integrated_20260923_14.xlsx
+++ b/data/trending_integrated_20260923_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4160</v>
+        <v>4195</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+25.49%</t>
+          <t>'+26.55%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>45114373812</v>
+        <v>47016521821</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1954</v>
+        <v>19360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.90%</t>
+          <t>'+24.74%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.39</v>
+        <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>139</v>
+        <v>396</v>
       </c>
       <c r="H3" t="n">
-        <v>1.02</v>
+        <v>0.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1603</v>
+        <v>15520</v>
       </c>
       <c r="K3" t="n">
-        <v>1603</v>
+        <v>15800</v>
       </c>
       <c r="L3" t="n">
-        <v>2030</v>
+        <v>19630</v>
       </c>
       <c r="M3" t="n">
-        <v>1585</v>
+        <v>15200</v>
       </c>
       <c r="N3" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>59845116275</v>
+        <v>114830819625</v>
       </c>
       <c r="P3" t="n">
-        <v>2465</v>
+        <v>34650</v>
       </c>
       <c r="Q3" t="n">
-        <v>865</v>
+        <v>6980</v>
       </c>
       <c r="R3" t="n">
-        <v>-400000</v>
+        <v>3000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 특허 플렉시블 PCB 확보 및 AI 데이터센터향 공급 확대 소식 기반의 주가 상승 기대.</t>
+          <t>NASA 및 스페이스X 선정, 11조원 포터블 X-Ray 시장 도전 등 다수의 호재 발표. 공매도 세력 약화 및 주가 급등 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['플렉시블 PCB', 'AI 데이터센터']</t>
+          <t>['NASA', '스페이스X']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>387690</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18670</v>
+        <v>1996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.30%</t>
+          <t>'+24.52%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.5</v>
+        <v>-0.39</v>
       </c>
       <c r="E4" t="n">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>366</v>
+        <v>142</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15520</v>
+        <v>1603</v>
       </c>
       <c r="K4" t="n">
-        <v>15800</v>
+        <v>1603</v>
       </c>
       <c r="L4" t="n">
-        <v>19150</v>
+        <v>2030</v>
       </c>
       <c r="M4" t="n">
-        <v>15200</v>
+        <v>1585</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="O4" t="n">
-        <v>100466300255</v>
+        <v>61846702808</v>
       </c>
       <c r="P4" t="n">
-        <v>34650</v>
+        <v>2465</v>
       </c>
       <c r="Q4" t="n">
-        <v>6980</v>
+        <v>865</v>
       </c>
       <c r="R4" t="n">
-        <v>3000</v>
+        <v>-400000</v>
       </c>
       <c r="S4" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>NASA 및 스페이스X 선정과 11조원 시장 도전 등 구체적인 사업 내용과 규모가 언급되며 높은 상승 기대감을 형성함.</t>
+          <t>미국 특허 플렉시블 PCB 확보 및 AI 데이터센터향 공급 확대 소식 기반의 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['스페이스X', 'X-ray']</t>
+          <t>['플렉시블 PCB', 'AI 데이터센터']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>387690</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -843,18 +843,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14420</v>
+        <v>14470</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.92%</t>
+          <t>'+11.31%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.42</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
         <v>50</v>
@@ -886,7 +886,7 @@
         <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>166183838830</v>
+        <v>167132258115</v>
       </c>
       <c r="P5" t="n">
         <v>25700</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18285</v>
+        <v>14430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.55%</t>
+          <t>'+10.74%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>-0.9</v>
       </c>
       <c r="E6" t="n">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="F6" t="n">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="G6" t="n">
-        <v>313</v>
+        <v>126</v>
       </c>
       <c r="H6" t="n">
-        <v>0.62</v>
+        <v>1.89</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>16540</v>
+        <v>13030</v>
       </c>
       <c r="K6" t="n">
-        <v>17530</v>
+        <v>12850</v>
       </c>
       <c r="L6" t="n">
-        <v>19950</v>
+        <v>16420</v>
       </c>
       <c r="M6" t="n">
-        <v>17500</v>
+        <v>12660</v>
       </c>
       <c r="N6" t="n">
-        <v>0.77</v>
+        <v>2.79</v>
       </c>
       <c r="O6" t="n">
-        <v>307686595195</v>
+        <v>126613930390</v>
       </c>
       <c r="P6" t="n">
-        <v>30550</v>
+        <v>64600</v>
       </c>
       <c r="Q6" t="n">
-        <v>6100</v>
+        <v>7520</v>
       </c>
       <c r="R6" t="n">
-        <v>-45000</v>
+        <v>-11000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-125000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등 소식과 함께 국내 양자 보안 테마의 상승 가능성을 언급하며 긍정적인 전망을 보이고 있습니다.</t>
+          <t>초소형위성 테마 관련 국방 과제 수주 발표. 주가 급등 및 하락에 대한 기대와 우려 공존.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['양자', '보안']</t>
+          <t>['초소형위성', '국방']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>478340</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14180</v>
+        <v>18210</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.83%</t>
+          <t>'+10.10%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.9</v>
+        <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="G7" t="n">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="H7" t="n">
-        <v>1.89</v>
+        <v>0.62</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13030</v>
+        <v>16540</v>
       </c>
       <c r="K7" t="n">
-        <v>12850</v>
+        <v>17530</v>
       </c>
       <c r="L7" t="n">
-        <v>16420</v>
+        <v>19950</v>
       </c>
       <c r="M7" t="n">
-        <v>12660</v>
+        <v>17500</v>
       </c>
       <c r="N7" t="n">
-        <v>2.79</v>
+        <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>123734270680</v>
+        <v>308942282985</v>
       </c>
       <c r="P7" t="n">
-        <v>64600</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>7520</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>-11000</v>
+        <v>-45000</v>
       </c>
       <c r="S7" t="n">
-        <v>-125000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>초소형 위성 관련 긍정적인 공시에도 불구하고, 주가 변동성에 대한 불안감과 단기적인 시세 차익에 대한 기대가 혼재함.</t>
+          <t>미국 양자 관련주 급등에 따른 국내 양자 보안 테마주 관심 증대. 주가 상승 및 하락에 대한 상반된 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['초소형 위성', '국방 과제']</t>
+          <t>['양자', '보안']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>478340</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7910</v>
+        <v>7880</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.94%</t>
+          <t>'+3.55%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1162,7 +1162,7 @@
         <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>90374138295</v>
+        <v>90864300175</v>
       </c>
       <c r="P8" t="n">
         <v>16200</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>219500</v>
+        <v>219000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.78%</t>
+          <t>'+3.55%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="H9" t="n">
         <v>75.51000000000001</v>
@@ -1254,7 +1254,7 @@
         <v>75.5</v>
       </c>
       <c r="O9" t="n">
-        <v>942389982500</v>
+        <v>961896061000</v>
       </c>
       <c r="P9" t="n">
         <v>243500</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>284500</v>
+        <v>284000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.89%</t>
+          <t>'+2.71%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G10" t="n">
-        <v>1824</v>
+        <v>1836</v>
       </c>
       <c r="H10" t="n">
         <v>46.55</v>
@@ -1346,7 +1346,7 @@
         <v>46.56</v>
       </c>
       <c r="O10" t="n">
-        <v>4010591889000</v>
+        <v>4079731371750</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>개인 투자자들의 긍정적인 기대감 속에서 주가 상승 전망이 있으나, 감정적인 표현과 정치적 언급이 다수 포함됨.</t>
+          <t>명절 후 중동 전쟁 리스크 소멸 시 주가 상승 전망. 이재명 대통령 지지 관련 내용 다수.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가 전망', '개미 투자']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13880</v>
+        <v>13940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.06%</t>
+          <t>'+2.50%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.16</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
         <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="H11" t="n">
         <v>9.609999999999999</v>
@@ -1438,7 +1438,7 @@
         <v>9.77</v>
       </c>
       <c r="O11" t="n">
-        <v>99703243065</v>
+        <v>100427595350</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31750</v>
+        <v>1848000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.11%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.62</v>
+        <v>-0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>479</v>
       </c>
       <c r="G12" t="n">
-        <v>165</v>
+        <v>1638</v>
       </c>
       <c r="H12" t="n">
-        <v>52.82</v>
+        <v>50.15</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>31400</v>
+        <v>1840000</v>
       </c>
       <c r="K12" t="n">
-        <v>31500</v>
+        <v>1899000</v>
       </c>
       <c r="L12" t="n">
-        <v>32100</v>
+        <v>1900000</v>
       </c>
       <c r="M12" t="n">
-        <v>31100</v>
+        <v>1836000</v>
       </c>
       <c r="N12" t="n">
-        <v>25.75</v>
+        <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>112491441900</v>
+        <v>4376146690000</v>
       </c>
       <c r="P12" t="n">
-        <v>32100</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>21000</v>
+        <v>333000</v>
       </c>
       <c r="R12" t="n">
-        <v>-81000</v>
+        <v>-536000</v>
       </c>
       <c r="S12" t="n">
-        <v>219000</v>
+        <v>91000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
+          <t>국내 증시 및 SK하이닉스 주가 부진에 대한 정부 비판. ADR 상승에도 하이닉스 주가 미반영.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '인천공항']</t>
+          <t>['ADR', '자사주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1845000</v>
+        <v>31500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.27%</t>
+          <t>'+0.32%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>56</v>
       </c>
       <c r="F13" t="n">
-        <v>482</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>1643</v>
+        <v>166</v>
       </c>
       <c r="H13" t="n">
-        <v>50.15</v>
+        <v>52.81</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,60 +1607,60 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1840000</v>
+        <v>31400</v>
       </c>
       <c r="K13" t="n">
-        <v>1899000</v>
+        <v>31500</v>
       </c>
       <c r="L13" t="n">
-        <v>1900000</v>
+        <v>32100</v>
       </c>
       <c r="M13" t="n">
-        <v>1836000</v>
+        <v>31100</v>
       </c>
       <c r="N13" t="n">
-        <v>50.17</v>
+        <v>25.75</v>
       </c>
       <c r="O13" t="n">
-        <v>4285120691000</v>
+        <v>114916207025</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>32100</v>
       </c>
       <c r="Q13" t="n">
-        <v>333000</v>
+        <v>21000</v>
       </c>
       <c r="R13" t="n">
-        <v>-536000</v>
+        <v>-81000</v>
       </c>
       <c r="S13" t="n">
-        <v>91000</v>
+        <v>219000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 업황 회복 기대감에도 불구하고, 주가 부진에 대한 불만과 정부 정책 비판 등 부정적인 심리가 지배적임.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '주가 관리']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8490</v>
+        <v>8480</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.24%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F14" t="n">
         <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H14" t="n">
         <v>26.63</v>
@@ -1714,7 +1714,7 @@
         <v>26.58</v>
       </c>
       <c r="O14" t="n">
-        <v>26219865670</v>
+        <v>26770228525</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3690</v>
+        <v>3685</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.94%</t>
+          <t>'-1.07%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.35</v>
       </c>
       <c r="E15" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F15" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G15" t="n">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="H15" t="n">
         <v>0.61</v>
@@ -1800,13 +1800,13 @@
         <v>4200</v>
       </c>
       <c r="M15" t="n">
-        <v>3675</v>
+        <v>3665</v>
       </c>
       <c r="N15" t="n">
         <v>0.96</v>
       </c>
       <c r="O15" t="n">
-        <v>68370687345</v>
+        <v>68683885725</v>
       </c>
       <c r="P15" t="n">
         <v>6300</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 급락에 대한 강한 불만과 함께, 종목 자체에 대한 부정적인 평가 및 투자자 이탈 움직임이 관찰됨.</t>
+          <t>주가 급락 및 물량 떠넘기기에 대한 불만. 단타 및 시총 소형 종목의 불안정성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['물량 떠넘기기', '단타']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17550</v>
+        <v>17600</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.46%</t>
+          <t>'-1.18%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F16" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G16" t="n">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="H16" t="n">
         <v>5.46</v>
@@ -1898,7 +1898,7 @@
         <v>6.22</v>
       </c>
       <c r="O16" t="n">
-        <v>139861146475</v>
+        <v>140945532865</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1958,13 +1958,13 @@
         <v>0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="F17" t="n">
         <v>209</v>
       </c>
       <c r="G17" t="n">
-        <v>2150</v>
+        <v>2211</v>
       </c>
       <c r="H17" t="n">
         <v>16.63</v>
@@ -1990,7 +1990,7 @@
         <v>16.42</v>
       </c>
       <c r="O17" t="n">
-        <v>12772201700</v>
+        <v>13105060975</v>
       </c>
       <c r="P17" t="n">
         <v>69200</v>
@@ -1999,7 +1999,7 @@
         <v>24150</v>
       </c>
       <c r="R17" t="n">
-        <v>-111000</v>
+        <v>-122000</v>
       </c>
       <c r="S17" t="n">
         <v>-3000</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30800</v>
+        <v>30750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.53%</t>
+          <t>'-2.69%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H18" t="n">
         <v>11.7</v>
@@ -2082,7 +2082,7 @@
         <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>79158989925</v>
+        <v>80085797275</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23100</v>
+        <v>22900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.55%</t>
+          <t>'-4.38%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F19" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H19" t="n">
         <v>1.68</v>
@@ -2174,7 +2174,7 @@
         <v>1.76</v>
       </c>
       <c r="O19" t="n">
-        <v>73479175300</v>
+        <v>74897626000</v>
       </c>
       <c r="P19" t="n">
         <v>39350</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48900</v>
+        <v>48800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.49%</t>
+          <t>'-4.69%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>73</v>
       </c>
       <c r="G20" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H20" t="n">
         <v>38.34</v>
@@ -2266,7 +2266,7 @@
         <v>38.44</v>
       </c>
       <c r="O20" t="n">
-        <v>88802086825</v>
+        <v>89972094700</v>
       </c>
       <c r="P20" t="n">
         <v>67300</v>
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="F21" t="n">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="G21" t="n">
-        <v>2012</v>
+        <v>2067</v>
       </c>
       <c r="H21" t="n">
         <v>23.03</v>
@@ -2358,7 +2358,7 @@
         <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>305321313750</v>
+        <v>310061616750</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 관련 긍정적 뉴스에도 불구하고, 주가 하락에 대한 불안감과 부정적인 전망이 혼재하며 투자자들의 혼란이 감지됨.</t>
+          <t>미국 원전 수주 관련 호재에도 불구하고 주가 하락 및 재료 소멸 우려. 개인 투자자들의 불만 표출.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '주가 조작']</t>
+          <t>['원전', 'SMR']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17380</v>
+        <v>17350</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.55%</t>
+          <t>'-7.71%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.09</v>
       </c>
       <c r="E22" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F22" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G22" t="n">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="H22" t="n">
         <v>10.38</v>
@@ -2444,13 +2444,13 @@
         <v>18800</v>
       </c>
       <c r="M22" t="n">
-        <v>17360</v>
+        <v>17350</v>
       </c>
       <c r="N22" t="n">
         <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>146797698550</v>
+        <v>149674263365</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>공매도 세력의 파산 가능성과 주가 조작 의혹 제기. 감사원 신고 및 수사 언급.</t>
+          <t>공매도 세력의 파산 및 마지막 저항 언급. 금융 당국 조사 관련 내용 포함.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['공매도', '주가조작', '감사원']</t>
+          <t>['공매도', '대차']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2650</v>
+        <v>2660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.15%</t>
+          <t>'-7.80%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="H23" t="n">
         <v>1.4</v>
@@ -2542,7 +2542,7 @@
         <v>0.48</v>
       </c>
       <c r="O23" t="n">
-        <v>22908801442</v>
+        <v>22961677197</v>
       </c>
       <c r="P23" t="n">
         <v>4760</v>

--- a/data/trending_integrated_20260923_14.xlsx
+++ b/data/trending_integrated_20260923_14.xlsx
@@ -578,13 +578,13 @@
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>47016521821</v>
+        <v>47959311409</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19360</v>
+        <v>19170</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+24.74%</t>
+          <t>'+23.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>114830819625</v>
+        <v>120603422395</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>NASA 및 스페이스X 선정, 11조원 포터블 X-Ray 시장 도전 등 다수의 호재 발표. 공매도 세력 약화 및 주가 급등 전망.</t>
+          <t>NASA 엑스레이 발생기 선정 및 스페이스X 협력 등 호재 연이은 부각. 인도발 수주 및 기술력 검증으로 시총 1조 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['NASA', '스페이스X']</t>
+          <t>['NASA', '스페이스X', '엑스레이']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1996</v>
+        <v>1946</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+24.52%</t>
+          <t>'+21.40%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.39</v>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H4" t="n">
         <v>1.02</v>
@@ -794,7 +794,7 @@
         <v>1.41</v>
       </c>
       <c r="O4" t="n">
-        <v>61846702808</v>
+        <v>64006172568</v>
       </c>
       <c r="P4" t="n">
         <v>2465</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14470</v>
+        <v>14400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.31%</t>
+          <t>'+10.77%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H5" t="n">
         <v>0.86</v>
@@ -886,7 +886,7 @@
         <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>167132258115</v>
+        <v>167891248565</v>
       </c>
       <c r="P5" t="n">
         <v>25700</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>나라스페이스테크놀로지</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14430</v>
+        <v>18260</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.74%</t>
+          <t>'+10.40%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.9</v>
+        <v>-0.15</v>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="F6" t="n">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="G6" t="n">
-        <v>126</v>
+        <v>322</v>
       </c>
       <c r="H6" t="n">
-        <v>1.89</v>
+        <v>0.62</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13030</v>
+        <v>16540</v>
       </c>
       <c r="K6" t="n">
-        <v>12850</v>
+        <v>17530</v>
       </c>
       <c r="L6" t="n">
-        <v>16420</v>
+        <v>19950</v>
       </c>
       <c r="M6" t="n">
-        <v>12660</v>
+        <v>17500</v>
       </c>
       <c r="N6" t="n">
-        <v>2.79</v>
+        <v>0.77</v>
       </c>
       <c r="O6" t="n">
-        <v>126613930390</v>
+        <v>310113832660</v>
       </c>
       <c r="P6" t="n">
-        <v>64600</v>
+        <v>30550</v>
       </c>
       <c r="Q6" t="n">
-        <v>7520</v>
+        <v>6100</v>
       </c>
       <c r="R6" t="n">
-        <v>-11000</v>
+        <v>-45000</v>
       </c>
       <c r="S6" t="n">
-        <v>-125000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>초소형위성 테마 관련 국방 과제 수주 발표. 주가 급등 및 하락에 대한 기대와 우려 공존.</t>
+          <t>미국 양자 관련주 급등에 따른 동반 상승 기대감. 양자 보안 기술 및 공매도 세력 관련 논의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['초소형위성', '국방']</t>
+          <t>['양자 보안', '아이온큐', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>478340</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>나라스페이스테크놀로지</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18210</v>
+        <v>14160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.10%</t>
+          <t>'+8.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.15</v>
+        <v>-0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="F7" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="G7" t="n">
-        <v>320</v>
+        <v>135</v>
       </c>
       <c r="H7" t="n">
-        <v>0.62</v>
+        <v>1.89</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16540</v>
+        <v>13030</v>
       </c>
       <c r="K7" t="n">
-        <v>17530</v>
+        <v>12850</v>
       </c>
       <c r="L7" t="n">
-        <v>19950</v>
+        <v>16420</v>
       </c>
       <c r="M7" t="n">
-        <v>17500</v>
+        <v>12660</v>
       </c>
       <c r="N7" t="n">
-        <v>0.77</v>
+        <v>2.79</v>
       </c>
       <c r="O7" t="n">
-        <v>308942282985</v>
+        <v>127920947655</v>
       </c>
       <c r="P7" t="n">
-        <v>30550</v>
+        <v>64600</v>
       </c>
       <c r="Q7" t="n">
-        <v>6100</v>
+        <v>7520</v>
       </c>
       <c r="R7" t="n">
-        <v>-45000</v>
+        <v>-11000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-125000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 국내 양자 보안 테마주 관심 증대. 주가 상승 및 하락에 대한 상반된 전망.</t>
+          <t>초소형 위성 자율 근접 운영 국방과제 주관 소식. 우주 항공 테마 기대감 및 투경/단일가 거래 방식 논의.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['양자', '보안']</t>
+          <t>['초소형 위성', '우주 항공', '국방']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>478340</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7880</v>
+        <v>7930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.55%</t>
+          <t>'+4.20%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.42</v>
       </c>
       <c r="E8" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F8" t="n">
         <v>58</v>
       </c>
       <c r="G8" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="H8" t="n">
         <v>1.9</v>
@@ -1162,7 +1162,7 @@
         <v>2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>90864300175</v>
+        <v>91372121440</v>
       </c>
       <c r="P8" t="n">
         <v>16200</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>219000</v>
+        <v>219500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.55%</t>
+          <t>'+3.78%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" t="n">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="H9" t="n">
         <v>75.51000000000001</v>
@@ -1254,7 +1254,7 @@
         <v>75.5</v>
       </c>
       <c r="O9" t="n">
-        <v>961896061000</v>
+        <v>983777661500</v>
       </c>
       <c r="P9" t="n">
         <v>243500</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>284000</v>
+        <v>284250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.71%</t>
+          <t>'+2.80%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="G10" t="n">
-        <v>1836</v>
+        <v>1853</v>
       </c>
       <c r="H10" t="n">
         <v>46.55</v>
@@ -1346,7 +1346,7 @@
         <v>46.56</v>
       </c>
       <c r="O10" t="n">
-        <v>4079731371750</v>
+        <v>4167197055500</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13940</v>
+        <v>13930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.50%</t>
+          <t>'+2.43%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="H11" t="n">
         <v>9.609999999999999</v>
@@ -1438,7 +1438,7 @@
         <v>9.77</v>
       </c>
       <c r="O11" t="n">
-        <v>100427595350</v>
+        <v>101399320005</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1848000</v>
+        <v>1854000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'+0.76%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="G12" t="n">
-        <v>1638</v>
+        <v>1668</v>
       </c>
       <c r="H12" t="n">
         <v>50.15</v>
@@ -1530,7 +1530,7 @@
         <v>50.17</v>
       </c>
       <c r="O12" t="n">
-        <v>4376146690000</v>
+        <v>4510513390500</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 증시 및 SK하이닉스 주가 부진에 대한 정부 비판. ADR 상승에도 하이닉스 주가 미반영.</t>
+          <t>미국 증시 상승 대비 국내 증시 부진 및 주가 관리 의혹 제기. 자사주 매입 외 매수세 부족.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['ADR', '자사주']</t>
+          <t>['반도체', '자사주 매입', '주가 관리']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,27 +1579,27 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31500</v>
+        <v>31550</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.32%</t>
+          <t>'+0.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H13" t="n">
-        <v>52.81</v>
+        <v>52.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>25.75</v>
       </c>
       <c r="O13" t="n">
-        <v>114916207025</v>
+        <v>117145044000</v>
       </c>
       <c r="P13" t="n">
         <v>32100</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8480</v>
+        <v>8510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="H14" t="n">
         <v>26.63</v>
@@ -1714,7 +1714,7 @@
         <v>26.58</v>
       </c>
       <c r="O14" t="n">
-        <v>26770228525</v>
+        <v>27532911290</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>LG디스플레이의 실적 개선 및 주가 상승 전망이 제기됨. 허수매도 및 주가 조작 의혹과 관련된 부정적 의견도 존재함.</t>
+          <t>유리 인터포저 및 게이밍 OLED 기술 부각. 실적 개선 및 목표 주가 상향 전망. 허수매도 의혹 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['LG디스플레이', '유리기판', 'OLED']</t>
+          <t>['OLED', '유리 인터포저', '실적']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3685</v>
+        <v>17660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.07%</t>
+          <t>'-0.84%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.35</v>
+        <v>-0.76</v>
       </c>
       <c r="E15" t="n">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="F15" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>491</v>
+        <v>927</v>
       </c>
       <c r="H15" t="n">
-        <v>0.61</v>
+        <v>5.46</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3725</v>
+        <v>17810</v>
       </c>
       <c r="K15" t="n">
-        <v>3740</v>
+        <v>17950</v>
       </c>
       <c r="L15" t="n">
-        <v>4200</v>
+        <v>18180</v>
       </c>
       <c r="M15" t="n">
-        <v>3665</v>
+        <v>17410</v>
       </c>
       <c r="N15" t="n">
-        <v>0.96</v>
+        <v>6.22</v>
       </c>
       <c r="O15" t="n">
-        <v>68683885725</v>
+        <v>142371974360</v>
       </c>
       <c r="P15" t="n">
-        <v>6300</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>1738</v>
+        <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>-176000</v>
+        <v>-273000</v>
       </c>
       <c r="S15" t="n">
-        <v>-5000</v>
+        <v>1000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 급락 및 물량 떠넘기기에 대한 불만. 단타 및 시총 소형 종목의 불안정성 언급.</t>
+          <t>명절 전 상승 기대감 속 2만원 돌파 시도 및 주포 활동 언급. 단타 세력의 빠른 이탈 촉구.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['물량 떠넘기기', '단타']</t>
+          <t>['코스닥', '주포', '단타']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17600</v>
+        <v>3685</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.18%</t>
+          <t>'-1.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.76</v>
+        <v>-0.35</v>
       </c>
       <c r="E16" t="n">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="F16" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G16" t="n">
-        <v>924</v>
+        <v>499</v>
       </c>
       <c r="H16" t="n">
-        <v>5.46</v>
+        <v>0.61</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17810</v>
+        <v>3725</v>
       </c>
       <c r="K16" t="n">
-        <v>17950</v>
+        <v>3740</v>
       </c>
       <c r="L16" t="n">
-        <v>18180</v>
+        <v>4200</v>
       </c>
       <c r="M16" t="n">
-        <v>17410</v>
+        <v>3665</v>
       </c>
       <c r="N16" t="n">
-        <v>6.22</v>
+        <v>0.96</v>
       </c>
       <c r="O16" t="n">
-        <v>140945532865</v>
+        <v>68889991120</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>6300</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>1738</v>
       </c>
       <c r="R16" t="n">
-        <v>-273000</v>
+        <v>-176000</v>
       </c>
       <c r="S16" t="n">
-        <v>1000</v>
+        <v>-5000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>명절 전 상승 기대감 속 2만원 돌파 시도 및 주포 활동 언급. 단타 세력의 빠른 이탈 촉구.</t>
+          <t>연이은 음봉 및 급락으로 인한 투자 심리 위축. 물량 떠넘기기 및 주포의 단기 매매 의혹.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['코스닥', '주포', '단타']</t>
+          <t>['단타', '물량 떠넘기기', '거래량']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -1958,13 +1958,13 @@
         <v>0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="F17" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="G17" t="n">
-        <v>2211</v>
+        <v>2258</v>
       </c>
       <c r="H17" t="n">
         <v>16.63</v>
@@ -1990,7 +1990,7 @@
         <v>16.42</v>
       </c>
       <c r="O17" t="n">
-        <v>13105060975</v>
+        <v>13502867400</v>
       </c>
       <c r="P17" t="n">
         <v>69200</v>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30750</v>
+        <v>30850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.69%</t>
+          <t>'-2.37%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G18" t="n">
         <v>134</v>
@@ -2082,7 +2082,7 @@
         <v>11.3</v>
       </c>
       <c r="O18" t="n">
-        <v>80085797275</v>
+        <v>81096171425</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2142,13 +2142,13 @@
         <v>-0.08</v>
       </c>
       <c r="E19" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G19" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H19" t="n">
         <v>1.68</v>
@@ -2174,7 +2174,7 @@
         <v>1.76</v>
       </c>
       <c r="O19" t="n">
-        <v>74897626000</v>
+        <v>75501556225</v>
       </c>
       <c r="P19" t="n">
         <v>39350</v>
@@ -2223,18 +2223,18 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48800</v>
+        <v>48900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.69%</t>
+          <t>'-4.49%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F20" t="n">
         <v>73</v>
@@ -2266,7 +2266,7 @@
         <v>38.44</v>
       </c>
       <c r="O20" t="n">
-        <v>89972094700</v>
+        <v>91731295425</v>
       </c>
       <c r="P20" t="n">
         <v>67300</v>
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="F21" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G21" t="n">
-        <v>2067</v>
+        <v>2124</v>
       </c>
       <c r="H21" t="n">
         <v>23.03</v>
@@ -2358,7 +2358,7 @@
         <v>23.05</v>
       </c>
       <c r="O21" t="n">
-        <v>310061616750</v>
+        <v>327220985350</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 원전 수주 관련 호재에도 불구하고 주가 하락 및 재료 소멸 우려. 개인 투자자들의 불만 표출.</t>
+          <t>미국형 원전 2기 확정 소식에도 재료 소멸 및 차트 붕괴 우려. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', 'SMR']</t>
+          <t>['원전', 'SMR', '차트']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17350</v>
+        <v>17340</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.71%</t>
+          <t>'-7.77%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.09</v>
       </c>
       <c r="E22" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F22" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G22" t="n">
-        <v>1195</v>
+        <v>1206</v>
       </c>
       <c r="H22" t="n">
         <v>10.38</v>
@@ -2444,13 +2444,13 @@
         <v>18800</v>
       </c>
       <c r="M22" t="n">
-        <v>17350</v>
+        <v>17330</v>
       </c>
       <c r="N22" t="n">
         <v>10.47</v>
       </c>
       <c r="O22" t="n">
-        <v>149674263365</v>
+        <v>153003962800</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2660</v>
+        <v>2630</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-7.80%</t>
+          <t>'-8.84%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.92</v>
       </c>
       <c r="E23" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" t="n">
         <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="H23" t="n">
         <v>1.4</v>
@@ -2542,7 +2542,7 @@
         <v>0.48</v>
       </c>
       <c r="O23" t="n">
-        <v>22961677197</v>
+        <v>23058481890</v>
       </c>
       <c r="P23" t="n">
         <v>4760</v>
